--- a/resources/product_sample.xlsx
+++ b/resources/product_sample.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\myproject\mallapi\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C46D3B7-B047-4FFD-8DC0-72641832ADD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3316D26-5D25-4FE8-9657-C1652D5AE720}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,15 +19,987 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>USER</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{47139AC4-4D3B-413A-8BD6-7C11F92600E1}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>USER:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>리테일</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>명</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{12FCD3A2-63AB-405F-8CDA-D2C2DEF7E8E4}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>USER:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>외부</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>상품</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> ID</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{30F3847B-7868-4074-998A-93921113DCB5}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>USER:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>치환된</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>브랜드명</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{58DCA746-AAF0-4448-BED3-0E096451C8E0}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>USER:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>상품명</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M1" authorId="0" shapeId="0" xr:uid="{EEFE46C0-5CA1-4E92-9CF2-D6CFA860121F}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>USER:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>이미지</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>링크</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>삽입</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N1" authorId="0" shapeId="0" xr:uid="{E5BFD3FA-EABB-4350-AA6C-32103694F12B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>USER:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>이미지</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>링크</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>삽입</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O1" authorId="0" shapeId="0" xr:uid="{A3DA6501-8A71-426E-B46F-8234BEA66C68}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>USER:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>이미지</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>링크</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>삽입</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P1" authorId="0" shapeId="0" xr:uid="{AF08EE49-C74B-4E1F-8EBD-69C8D7C6DBFA}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>USER:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>이미지</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>링크</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>삽입</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q1" authorId="0" shapeId="0" xr:uid="{19E971A1-ED50-4ACA-9DA6-3FF96D2C2943}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>USER:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+COST</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="R1" authorId="0" shapeId="0" xr:uid="{D46E1C07-B751-4D75-8B55-F6F2D4224880}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>USER:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>공급가</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>(EU)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="S1" authorId="0" shapeId="0" xr:uid="{4E0E94D9-27FB-44EE-99FB-2A40DD70452D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>USER:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>판매</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>원화가</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V1" authorId="0" shapeId="0" xr:uid="{59E259A2-D671-40D1-AB9B-391C496B7F54}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>USER:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>소비자가</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>(EU)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="W1" authorId="0" shapeId="0" xr:uid="{0C1C0849-67EE-47FE-AF9C-03084BD01A3F}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>USER:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>소비자</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>원화가</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Y1" authorId="0" shapeId="0" xr:uid="{263FCA83-75FA-438D-A966-D2C6F4816137}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>USER:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>옵션별</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> ID</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AB1" authorId="0" shapeId="0" xr:uid="{9BB618FA-8A47-49B5-A42F-D1181A993A19}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>USER:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>옵션별</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>판매가</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>(</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>원화</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">)
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AC1" authorId="0" shapeId="0" xr:uid="{B51028BA-C6FA-43B6-87BD-122D351F1ADA}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>USER:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>옵션가</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> - cost
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AD1" authorId="0" shapeId="0" xr:uid="{9A074662-64A6-46AB-B899-4CFBAA0DC4E5}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">USER:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>판매</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>링크</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AE1" authorId="0" shapeId="0" xr:uid="{5FE69B54-4428-4A3B-9942-182CA64D23D7}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>USER:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>상태</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="65">
   <si>
     <t>external_product_id</t>
   </si>
   <si>
-    <t>raw_brand_name</t>
-  </si>
-  <si>
     <t>product_name</t>
   </si>
   <si>
@@ -109,9 +1081,6 @@
     <t>GUCCI</t>
   </si>
   <si>
-    <t>GG 로고 티셔츠</t>
-  </si>
-  <si>
     <t>남성</t>
   </si>
   <si>
@@ -167,9 +1136,6 @@
   </si>
   <si>
     <t>PRADA</t>
-  </si>
-  <si>
-    <t>프라다 나일론 백팩</t>
   </si>
   <si>
     <t>여성</t>
@@ -212,15 +1178,23 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>calculated_price_krw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>markup</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>retailer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>manual_retail_price_krw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>manual_price_krw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>샘플</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -228,7 +1202,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -243,8 +1217,36 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -254,6 +1256,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -270,9 +1278,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -574,23 +1583,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AD4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AE4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="20" max="20" width="14.625" customWidth="1"/>
-    <col min="21" max="21" width="9.625" customWidth="1"/>
+    <col min="19" max="19" width="14.625" customWidth="1"/>
+    <col min="20" max="20" width="9.625" customWidth="1"/>
+    <col min="28" max="28" width="17.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D1" t="s">
         <v>1</v>
@@ -631,300 +1641,322 @@
       <c r="P1" t="s">
         <v>13</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" t="s">
         <v>15</v>
       </c>
       <c r="S1" t="s">
+        <v>63</v>
+      </c>
+      <c r="T1" t="s">
+        <v>60</v>
+      </c>
+      <c r="U1" t="s">
         <v>16</v>
-      </c>
-      <c r="T1" t="s">
-        <v>63</v>
-      </c>
-      <c r="U1" t="s">
-        <v>64</v>
       </c>
       <c r="V1" t="s">
         <v>17</v>
       </c>
       <c r="W1" t="s">
+        <v>62</v>
+      </c>
+      <c r="X1" t="s">
         <v>18</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>20</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE1" t="s">
         <v>19</v>
       </c>
-      <c r="Y1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Z1" t="s">
-        <v>21</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>22</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>23</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>24</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>20</v>
+      <c r="B2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2">
+        <v>300</v>
+      </c>
+      <c r="R2" s="2">
+        <v>420</v>
+      </c>
+      <c r="S2" s="2">
+        <v>200000</v>
+      </c>
+      <c r="T2" s="2">
+        <v>1</v>
+      </c>
+      <c r="U2" s="2">
+        <v>10</v>
+      </c>
+      <c r="V2" s="2">
+        <v>700</v>
+      </c>
+      <c r="W2" s="2">
+        <v>300000</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA2" s="2">
+        <v>10</v>
+      </c>
+      <c r="AB2" s="2">
+        <v>200000</v>
+      </c>
+      <c r="AC2" s="2">
+        <v>420</v>
+      </c>
+      <c r="AD2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AE2" s="2" t="s">
+        <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C3" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D3" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="F3" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G3" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H3" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I3" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J3" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K3" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L3" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M3" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2">
+        <v>300</v>
+      </c>
+      <c r="R3" s="2">
+        <v>420</v>
+      </c>
+      <c r="S3" s="2">
+        <v>200000</v>
+      </c>
+      <c r="T3" s="2">
+        <v>1</v>
+      </c>
+      <c r="U3" s="2">
+        <v>10</v>
+      </c>
+      <c r="V3" s="2">
+        <v>700</v>
+      </c>
+      <c r="W3" s="2">
+        <v>300000</v>
+      </c>
+      <c r="X3" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="N2" t="s">
+      <c r="Y3" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA3" s="2">
+        <v>5</v>
+      </c>
+      <c r="AB3" s="2">
+        <v>200000</v>
+      </c>
+      <c r="AC3" s="2">
+        <v>420</v>
+      </c>
+      <c r="AD3" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE3" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="R2">
-        <v>300</v>
-      </c>
-      <c r="S2">
-        <v>420</v>
-      </c>
-      <c r="T2">
+    </row>
+    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2">
+        <v>700</v>
+      </c>
+      <c r="R4" s="2">
+        <v>920</v>
+      </c>
+      <c r="S4" s="2">
         <v>200000</v>
       </c>
-      <c r="U2">
+      <c r="T4" s="2">
         <v>1</v>
       </c>
-      <c r="V2">
-        <v>10</v>
-      </c>
-      <c r="W2">
-        <v>580000</v>
-      </c>
-      <c r="X2" t="s">
-        <v>39</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>43</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA2">
-        <v>10</v>
-      </c>
-      <c r="AB2">
-        <v>580000</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>42</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G3" t="s">
-        <v>31</v>
-      </c>
-      <c r="H3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I3" t="s">
-        <v>33</v>
-      </c>
-      <c r="J3" t="s">
-        <v>34</v>
-      </c>
-      <c r="K3" t="s">
-        <v>35</v>
-      </c>
-      <c r="L3" t="s">
-        <v>36</v>
-      </c>
-      <c r="M3" t="s">
-        <v>37</v>
-      </c>
-      <c r="N3" t="s">
+      <c r="U4" s="2">
+        <v>5</v>
+      </c>
+      <c r="V4" s="2">
+        <v>900</v>
+      </c>
+      <c r="W4" s="2">
+        <v>500000</v>
+      </c>
+      <c r="X4" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="Y4" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z4" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA4" s="2">
+        <v>3</v>
+      </c>
+      <c r="AB4" s="2">
+        <v>200000</v>
+      </c>
+      <c r="AC4" s="2">
+        <v>920</v>
+      </c>
+      <c r="AD4" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AE4" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="R3">
-        <v>300</v>
-      </c>
-      <c r="S3">
-        <v>420</v>
-      </c>
-      <c r="T3">
-        <v>200000</v>
-      </c>
-      <c r="U3">
-        <v>1</v>
-      </c>
-      <c r="V3">
-        <v>10</v>
-      </c>
-      <c r="W3">
-        <v>580000</v>
-      </c>
-      <c r="X3" t="s">
-        <v>39</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>46</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA3">
-        <v>5</v>
-      </c>
-      <c r="AB3">
-        <v>580000</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D4" t="s">
-        <v>48</v>
-      </c>
-      <c r="E4" t="s">
-        <v>49</v>
-      </c>
-      <c r="F4" t="s">
-        <v>50</v>
-      </c>
-      <c r="G4" t="s">
-        <v>51</v>
-      </c>
-      <c r="H4" t="s">
-        <v>52</v>
-      </c>
-      <c r="I4" t="s">
-        <v>53</v>
-      </c>
-      <c r="J4" t="s">
-        <v>54</v>
-      </c>
-      <c r="K4" t="s">
-        <v>55</v>
-      </c>
-      <c r="L4" t="s">
-        <v>36</v>
-      </c>
-      <c r="M4" t="s">
-        <v>56</v>
-      </c>
-      <c r="N4" t="s">
-        <v>57</v>
-      </c>
-      <c r="R4">
-        <v>700</v>
-      </c>
-      <c r="S4">
-        <v>920</v>
-      </c>
-      <c r="T4">
-        <v>200000</v>
-      </c>
-      <c r="U4">
-        <v>1</v>
-      </c>
-      <c r="V4">
-        <v>5</v>
-      </c>
-      <c r="W4">
-        <v>1200000</v>
-      </c>
-      <c r="X4" t="s">
-        <v>58</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>61</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>59</v>
-      </c>
-      <c r="AA4">
-        <v>3</v>
-      </c>
-      <c r="AB4">
-        <v>1200000</v>
-      </c>
-      <c r="AC4" t="s">
-        <v>60</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>40</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>